--- a/deploy_app/sample_data/projects/p2p_028/engagement_workbook.xlsx
+++ b/deploy_app/sample_data/projects/p2p_028/engagement_workbook.xlsx
@@ -6708,7 +6708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -6789,15 +6789,15 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>73810153</t>
+          <t>70983537</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>270004</v>
+        <v>-4750.06</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Under threshold</t>
         </is>
       </c>
     </row>
@@ -6807,15 +6807,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>73324525</t>
+          <t>72536840</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26713.29</v>
+        <v>73501.19</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Under threshold</t>
+          <t>Check</t>
         </is>
       </c>
     </row>
@@ -6825,11 +6825,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>70298549</t>
+          <t>72240345</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>301007.5</v>
+        <v>239062.82</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -6843,11 +6843,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>73765693</t>
+          <t>70658745</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>314751.57</v>
+        <v>128646.29</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -6861,373 +6861,13 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>70618959</t>
+          <t>72435169</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>193281.77</v>
+        <v>47040.06</v>
       </c>
       <c r="D13" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>6</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>71459454</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>382654.58</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>7</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>70442662</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>-6874.95</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Under threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>8</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>72240345</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>239062.82</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>9</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>72416806</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>34405.62</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Under threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>10</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>70658745</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>128646.29</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>11</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>72925180</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>-38310.76</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Under threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>12</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>72840877</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>16492.94</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Under threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>13</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>72462572</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>46191.11</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Under threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>14</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>70427405</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>7275.73</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Under threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>15</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>70936213</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>19082.49</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Under threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>16</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>73163483</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>-37098.82</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Under threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>17</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>72536840</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>73501.19</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>18</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>73354969</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>33960.6</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Under threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>19</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>73055739</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>8305.129999999999</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Under threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>20</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>73963830</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>-92.27</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Under threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>21</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>71058103</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>38803.55</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Under threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>22</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>70606672</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>101552.33</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>23</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>73243567</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>-13567.3</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Under threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>24</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>70099255</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>374115.59</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>25</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>70484142</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>29872.03</v>
-      </c>
-      <c r="D33" t="inlineStr">
         <is>
           <t>Under threshold</t>
         </is>
